--- a/02_DIA_inicio_2026_analisis_assets/rbd_9741_escuela-basica-republica-de-indonesia_nt2_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9741_escuela-basica-republica-de-indonesia_nt2_rubricas.xlsx
@@ -1992,13 +1992,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{150FE9ED-A558-4230-BA93-2A9898348C48}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3193718C-9B25-4C33-B4B2-634755FF7F40}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0F16DDF0-EFFD-48EA-AFE1-DAE4DC8B3B88}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BD6D278F-D60A-48BF-B688-B4C0182AD669}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1ACA183D-11E3-4AB4-9876-EFCCAF0DC237}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1C32A4D7-8DAE-4E9C-8177-D9A9C5DCA4D7}"/>
 </file>